--- a/06_Office_Related/01_NSO_work/06_SL_processing/03_TN_SL_2026-27/SL 2.0/Ariyalur.xlsx
+++ b/06_Office_Related/01_NSO_work/06_SL_processing/03_TN_SL_2026-27/SL 2.0/Ariyalur.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05 GIT\01_masterRepo\06_Office_Related\01_NSO_work\06_SL_to_PIVOT_to_Compare_with_WP\TN WP 2026-27\SL 2.0\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05 GIT\01_masterRepo\06_Office_Related\01_NSO_work\06_SL_processing\03_TN_SL_2026-27\SL 2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FFAF5D4-5283-4087-A060-1EAEC952621E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3088C6C9-CFF6-4A61-89C7-BBAE3596ED8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="125">
   <si>
     <t>State Sample</t>
   </si>
@@ -410,9 +410,6 @@
   </si>
   <si>
     <t>#  = Group' B' Village,   @ = Group ' A ' Village</t>
-  </si>
-  <si>
-    <t>9</t>
   </si>
   <si>
     <t xml:space="preserve">           BLACKGRAM     ( R- UI)   Shortfall 4 villages  adjusted for  THIRUVARUR district</t>
@@ -783,15 +780,18 @@
     <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -816,8 +816,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -839,12 +842,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1167,104 +1164,104 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="25" customHeight="1">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="66" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
     </row>
     <row r="2" spans="1:14" ht="25" customHeight="1">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
     </row>
     <row r="3" spans="1:14" s="6" customFormat="1" ht="25" customHeight="1">
-      <c r="A3" s="73" t="s">
+      <c r="A3" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73" t="s">
+      <c r="B3" s="66"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
-      <c r="K3" s="73"/>
-      <c r="L3" s="73"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="66"/>
+      <c r="K3" s="66"/>
+      <c r="L3" s="66"/>
     </row>
     <row r="4" spans="1:14" ht="25" customHeight="1">
-      <c r="A4" s="74" t="s">
+      <c r="A4" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="74"/>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="74" t="s">
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67" t="s">
         <v>112</v>
       </c>
-      <c r="K4" s="74"/>
-      <c r="L4" s="74"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
     </row>
     <row r="5" spans="1:14" ht="46.55" customHeight="1">
-      <c r="A5" s="67" t="s">
+      <c r="A5" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="71" t="s">
+      <c r="B5" s="73" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="68" t="s">
+      <c r="C5" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="69"/>
-      <c r="E5" s="70"/>
-      <c r="F5" s="66" t="s">
+      <c r="D5" s="71"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66" t="s">
+      <c r="G5" s="68"/>
+      <c r="H5" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="66"/>
-      <c r="J5" s="66" t="s">
+      <c r="I5" s="68"/>
+      <c r="J5" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="K5" s="66"/>
-      <c r="L5" s="66" t="s">
+      <c r="K5" s="68"/>
+      <c r="L5" s="68" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="35.35" customHeight="1">
-      <c r="A6" s="67"/>
-      <c r="B6" s="72"/>
+      <c r="A6" s="69"/>
+      <c r="B6" s="74"/>
       <c r="C6" s="7" t="s">
         <v>7</v>
       </c>
@@ -1292,7 +1289,7 @@
       <c r="K6" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="L6" s="66"/>
+      <c r="L6" s="68"/>
     </row>
     <row r="7" spans="1:14" ht="61.5" customHeight="1">
       <c r="A7" s="4">
@@ -1607,12 +1604,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="G3:L3"/>
-    <mergeCell ref="J4:L4"/>
     <mergeCell ref="L5:L6"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="F5:G5"/>
@@ -1620,6 +1611,12 @@
     <mergeCell ref="J5:K5"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="B5:B6"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="G3:L3"/>
+    <mergeCell ref="J4:L4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
@@ -1632,7 +1629,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U44"/>
+  <dimension ref="A1:U36"/>
   <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="1" max="1" width="23.75" style="8" customWidth="1"/>
@@ -3160,134 +3157,134 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="13.6">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="56"/>
-      <c r="T1" s="56"/>
-      <c r="U1" s="56"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="54"/>
+      <c r="S1" s="54"/>
+      <c r="T1" s="54"/>
+      <c r="U1" s="54"/>
     </row>
     <row r="2" spans="1:21" ht="13.6">
-      <c r="A2" s="56" t="s">
+      <c r="A2" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="56"/>
-      <c r="R2" s="56"/>
-      <c r="S2" s="56"/>
-      <c r="T2" s="56"/>
-      <c r="U2" s="56"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
+      <c r="N2" s="54"/>
+      <c r="O2" s="54"/>
+      <c r="P2" s="54"/>
+      <c r="Q2" s="54"/>
+      <c r="R2" s="54"/>
+      <c r="S2" s="54"/>
+      <c r="T2" s="54"/>
+      <c r="U2" s="54"/>
     </row>
     <row r="3" spans="1:21" ht="13.6">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="56" t="s">
+      <c r="G3" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
-      <c r="L3" s="56"/>
-      <c r="M3" s="56"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
       <c r="P3" s="9"/>
-      <c r="Q3" s="56" t="s">
+      <c r="Q3" s="54" t="s">
         <v>50</v>
       </c>
-      <c r="R3" s="56"/>
-      <c r="S3" s="56"/>
-      <c r="T3" s="56"/>
-      <c r="U3" s="56"/>
+      <c r="R3" s="54"/>
+      <c r="S3" s="54"/>
+      <c r="T3" s="54"/>
+      <c r="U3" s="54"/>
     </row>
     <row r="4" spans="1:21" ht="40.75">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="54" t="s">
+      <c r="B4" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="55" t="s">
+      <c r="C4" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55" t="s">
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55" t="s">
+      <c r="G4" s="57"/>
+      <c r="H4" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55" t="s">
+      <c r="I4" s="57"/>
+      <c r="J4" s="57" t="s">
         <v>80</v>
       </c>
-      <c r="K4" s="55"/>
-      <c r="L4" s="62" t="s">
-        <v>125</v>
-      </c>
-      <c r="M4" s="63"/>
-      <c r="N4" s="55" t="s">
+      <c r="K4" s="57"/>
+      <c r="L4" s="63" t="s">
+        <v>124</v>
+      </c>
+      <c r="M4" s="64"/>
+      <c r="N4" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="O4" s="55"/>
-      <c r="P4" s="62" t="s">
+      <c r="O4" s="57"/>
+      <c r="P4" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="Q4" s="64"/>
+      <c r="Q4" s="65"/>
       <c r="R4" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="S4" s="54" t="s">
+      <c r="S4" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="T4" s="54"/>
-      <c r="U4" s="54" t="s">
+      <c r="T4" s="56"/>
+      <c r="U4" s="56" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="27.2">
-      <c r="A5" s="54"/>
-      <c r="B5" s="54"/>
+      <c r="A5" s="56"/>
+      <c r="B5" s="56"/>
       <c r="C5" s="11" t="s">
         <v>21</v>
       </c>
@@ -3342,11 +3339,11 @@
       <c r="T5" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="U5" s="54"/>
+      <c r="U5" s="56"/>
     </row>
     <row r="6" spans="1:21" s="13" customFormat="1" ht="38.75">
-      <c r="A6" s="54"/>
-      <c r="B6" s="54"/>
+      <c r="A6" s="56"/>
+      <c r="B6" s="56"/>
       <c r="C6" s="12" t="s">
         <v>26</v>
       </c>
@@ -3406,29 +3403,29 @@
       </c>
     </row>
     <row r="7" spans="1:21" ht="13.6">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="58"/>
-      <c r="C7" s="58"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="58"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="58"/>
-      <c r="K7" s="58"/>
-      <c r="L7" s="58"/>
-      <c r="M7" s="58"/>
-      <c r="N7" s="58"/>
-      <c r="O7" s="58"/>
-      <c r="P7" s="58"/>
-      <c r="Q7" s="58"/>
-      <c r="R7" s="58"/>
-      <c r="S7" s="58"/>
-      <c r="T7" s="58"/>
-      <c r="U7" s="58"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="59"/>
+      <c r="K7" s="59"/>
+      <c r="L7" s="59"/>
+      <c r="M7" s="59"/>
+      <c r="N7" s="59"/>
+      <c r="O7" s="59"/>
+      <c r="P7" s="59"/>
+      <c r="Q7" s="59"/>
+      <c r="R7" s="59"/>
+      <c r="S7" s="59"/>
+      <c r="T7" s="59"/>
+      <c r="U7" s="59"/>
     </row>
     <row r="8" spans="1:21" ht="13.6">
       <c r="A8" s="28" t="s">
@@ -3582,29 +3579,29 @@
       <c r="U12" s="11"/>
     </row>
     <row r="13" spans="1:21" ht="13.6">
-      <c r="A13" s="59" t="s">
+      <c r="A13" s="60" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="60"/>
-      <c r="C13" s="60"/>
-      <c r="D13" s="60"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="60"/>
-      <c r="J13" s="60"/>
-      <c r="K13" s="60"/>
-      <c r="L13" s="60"/>
-      <c r="M13" s="60"/>
-      <c r="N13" s="60"/>
-      <c r="O13" s="60"/>
-      <c r="P13" s="60"/>
-      <c r="Q13" s="60"/>
-      <c r="R13" s="60"/>
-      <c r="S13" s="60"/>
-      <c r="T13" s="60"/>
-      <c r="U13" s="60"/>
+      <c r="B13" s="61"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="61"/>
+      <c r="F13" s="61"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="61"/>
+      <c r="I13" s="61"/>
+      <c r="J13" s="61"/>
+      <c r="K13" s="61"/>
+      <c r="L13" s="61"/>
+      <c r="M13" s="61"/>
+      <c r="N13" s="61"/>
+      <c r="O13" s="61"/>
+      <c r="P13" s="61"/>
+      <c r="Q13" s="61"/>
+      <c r="R13" s="61"/>
+      <c r="S13" s="61"/>
+      <c r="T13" s="61"/>
+      <c r="U13" s="61"/>
     </row>
     <row r="14" spans="1:21" ht="13.6">
       <c r="A14" s="28" t="s">
@@ -4161,7 +4158,7 @@
     </row>
     <row r="33" spans="1:21" ht="13.6">
       <c r="A33" s="29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B33" s="30"/>
       <c r="C33" s="31"/>
@@ -4185,27 +4182,27 @@
       <c r="U33" s="31"/>
     </row>
     <row r="34" spans="1:21">
-      <c r="A34" s="61"/>
-      <c r="B34" s="61"/>
-      <c r="C34" s="61"/>
-      <c r="D34" s="61"/>
-      <c r="E34" s="61"/>
-      <c r="F34" s="61"/>
-      <c r="G34" s="61"/>
-      <c r="H34" s="61"/>
-      <c r="I34" s="61"/>
-      <c r="J34" s="61"/>
-      <c r="K34" s="61"/>
-      <c r="L34" s="61"/>
-      <c r="M34" s="61"/>
-      <c r="N34" s="61"/>
-      <c r="O34" s="61"/>
-      <c r="P34" s="61"/>
-      <c r="Q34" s="61"/>
-      <c r="R34" s="61"/>
-      <c r="S34" s="61"/>
-      <c r="T34" s="61"/>
-      <c r="U34" s="61"/>
+      <c r="A34" s="62"/>
+      <c r="B34" s="62"/>
+      <c r="C34" s="62"/>
+      <c r="D34" s="62"/>
+      <c r="E34" s="62"/>
+      <c r="F34" s="62"/>
+      <c r="G34" s="62"/>
+      <c r="H34" s="62"/>
+      <c r="I34" s="62"/>
+      <c r="J34" s="62"/>
+      <c r="K34" s="62"/>
+      <c r="L34" s="62"/>
+      <c r="M34" s="62"/>
+      <c r="N34" s="62"/>
+      <c r="O34" s="62"/>
+      <c r="P34" s="62"/>
+      <c r="Q34" s="62"/>
+      <c r="R34" s="62"/>
+      <c r="S34" s="62"/>
+      <c r="T34" s="62"/>
+      <c r="U34" s="62"/>
     </row>
     <row r="35" spans="1:21" ht="13.6">
       <c r="A35" s="41" t="s">
@@ -4228,10 +4225,10 @@
       <c r="P35" s="41"/>
       <c r="Q35" s="44"/>
       <c r="R35" s="41"/>
-      <c r="S35" s="56" t="s">
+      <c r="S35" s="54" t="s">
         <v>121</v>
       </c>
-      <c r="T35" s="56"/>
+      <c r="T35" s="54"/>
       <c r="U35" s="9"/>
     </row>
     <row r="36" spans="1:21">
@@ -4239,18 +4236,8 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="1:21">
-      <c r="A44" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A2:U2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="G3:M3"/>
-    <mergeCell ref="Q3:U3"/>
     <mergeCell ref="B4:B6"/>
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="F4:G4"/>
@@ -4266,6 +4253,11 @@
     <mergeCell ref="S4:T4"/>
     <mergeCell ref="U4:U5"/>
     <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="G3:M3"/>
+    <mergeCell ref="Q3:U3"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.31496062992126" right="0.31496062992126" top="0.35433070866141703" bottom="0.35433070866141703" header="0.31496062992126" footer="0.31496062992126"/>
@@ -5798,134 +5790,134 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="13.6">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="56"/>
-      <c r="T1" s="56"/>
-      <c r="U1" s="56"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="54"/>
+      <c r="S1" s="54"/>
+      <c r="T1" s="54"/>
+      <c r="U1" s="54"/>
     </row>
     <row r="2" spans="1:21" ht="13.6">
-      <c r="A2" s="56" t="s">
+      <c r="A2" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="56"/>
-      <c r="R2" s="56"/>
-      <c r="S2" s="56"/>
-      <c r="T2" s="56"/>
-      <c r="U2" s="56"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
+      <c r="N2" s="54"/>
+      <c r="O2" s="54"/>
+      <c r="P2" s="54"/>
+      <c r="Q2" s="54"/>
+      <c r="R2" s="54"/>
+      <c r="S2" s="54"/>
+      <c r="T2" s="54"/>
+      <c r="U2" s="54"/>
     </row>
     <row r="3" spans="1:21" ht="13.6">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="56" t="s">
+      <c r="G3" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
-      <c r="L3" s="56"/>
-      <c r="M3" s="56"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
       <c r="P3" s="9"/>
-      <c r="Q3" s="56" t="s">
+      <c r="Q3" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="R3" s="56"/>
-      <c r="S3" s="56"/>
-      <c r="T3" s="56"/>
-      <c r="U3" s="56"/>
+      <c r="R3" s="54"/>
+      <c r="S3" s="54"/>
+      <c r="T3" s="54"/>
+      <c r="U3" s="54"/>
     </row>
     <row r="4" spans="1:21" ht="40.75">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="54" t="s">
+      <c r="B4" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="55" t="s">
+      <c r="C4" s="57" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55" t="s">
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57" t="s">
         <v>109</v>
       </c>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55" t="s">
+      <c r="G4" s="57"/>
+      <c r="H4" s="57" t="s">
         <v>37</v>
       </c>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55" t="s">
+      <c r="I4" s="57"/>
+      <c r="J4" s="57" t="s">
         <v>80</v>
       </c>
-      <c r="K4" s="55"/>
-      <c r="L4" s="54" t="s">
+      <c r="K4" s="57"/>
+      <c r="L4" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="M4" s="54"/>
-      <c r="N4" s="54" t="s">
+      <c r="M4" s="56"/>
+      <c r="N4" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="O4" s="54"/>
-      <c r="P4" s="62" t="s">
+      <c r="O4" s="56"/>
+      <c r="P4" s="63" t="s">
         <v>105</v>
       </c>
-      <c r="Q4" s="64"/>
+      <c r="Q4" s="65"/>
       <c r="R4" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="S4" s="54" t="s">
+      <c r="S4" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="T4" s="54"/>
-      <c r="U4" s="54" t="s">
+      <c r="T4" s="56"/>
+      <c r="U4" s="56" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="27.2">
-      <c r="A5" s="54"/>
-      <c r="B5" s="54"/>
+      <c r="A5" s="56"/>
+      <c r="B5" s="56"/>
       <c r="C5" s="11" t="s">
         <v>21</v>
       </c>
@@ -5980,11 +5972,11 @@
       <c r="T5" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="U5" s="54"/>
+      <c r="U5" s="56"/>
     </row>
     <row r="6" spans="1:21" s="13" customFormat="1" ht="25.85">
-      <c r="A6" s="54"/>
-      <c r="B6" s="54"/>
+      <c r="A6" s="56"/>
+      <c r="B6" s="56"/>
       <c r="C6" s="12" t="s">
         <v>26</v>
       </c>
@@ -6044,29 +6036,29 @@
       </c>
     </row>
     <row r="7" spans="1:21" ht="13.6">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="58"/>
-      <c r="C7" s="58"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="58"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="58"/>
-      <c r="K7" s="58"/>
-      <c r="L7" s="58"/>
-      <c r="M7" s="58"/>
-      <c r="N7" s="58"/>
-      <c r="O7" s="58"/>
-      <c r="P7" s="58"/>
-      <c r="Q7" s="58"/>
-      <c r="R7" s="58"/>
-      <c r="S7" s="58"/>
-      <c r="T7" s="58"/>
-      <c r="U7" s="58"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="59"/>
+      <c r="K7" s="59"/>
+      <c r="L7" s="59"/>
+      <c r="M7" s="59"/>
+      <c r="N7" s="59"/>
+      <c r="O7" s="59"/>
+      <c r="P7" s="59"/>
+      <c r="Q7" s="59"/>
+      <c r="R7" s="59"/>
+      <c r="S7" s="59"/>
+      <c r="T7" s="59"/>
+      <c r="U7" s="59"/>
     </row>
     <row r="8" spans="1:21" ht="13.6">
       <c r="A8" s="28" t="s">
@@ -6191,29 +6183,29 @@
       <c r="U11" s="11"/>
     </row>
     <row r="12" spans="1:21" ht="13.6">
-      <c r="A12" s="59" t="s">
+      <c r="A12" s="60" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="60"/>
-      <c r="C12" s="60"/>
-      <c r="D12" s="60"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60"/>
-      <c r="H12" s="60"/>
-      <c r="I12" s="60"/>
-      <c r="J12" s="60"/>
-      <c r="K12" s="60"/>
-      <c r="L12" s="60"/>
-      <c r="M12" s="60"/>
-      <c r="N12" s="60"/>
-      <c r="O12" s="60"/>
-      <c r="P12" s="60"/>
-      <c r="Q12" s="60"/>
-      <c r="R12" s="60"/>
-      <c r="S12" s="60"/>
-      <c r="T12" s="60"/>
-      <c r="U12" s="60"/>
+      <c r="B12" s="61"/>
+      <c r="C12" s="61"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="61"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="61"/>
+      <c r="M12" s="61"/>
+      <c r="N12" s="61"/>
+      <c r="O12" s="61"/>
+      <c r="P12" s="61"/>
+      <c r="Q12" s="61"/>
+      <c r="R12" s="61"/>
+      <c r="S12" s="61"/>
+      <c r="T12" s="61"/>
+      <c r="U12" s="61"/>
     </row>
     <row r="13" spans="1:21" ht="13.6">
       <c r="A13" s="14" t="s">
@@ -6404,11 +6396,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A2:U2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="G3:M3"/>
-    <mergeCell ref="Q3:U3"/>
     <mergeCell ref="A7:U7"/>
     <mergeCell ref="A12:U12"/>
     <mergeCell ref="J4:K4"/>
@@ -6422,6 +6409,11 @@
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="H4:I4"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="G3:M3"/>
+    <mergeCell ref="Q3:U3"/>
   </mergeCells>
   <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="75" orientation="landscape" r:id="rId1"/>
